--- a/output_6_comparison.xlsx
+++ b/output_6_comparison.xlsx
@@ -515,7 +515,7 @@
         <v>2000</v>
       </c>
       <c r="H2" t="n">
-        <v>21180</v>
+        <v>21180.00000000001</v>
       </c>
       <c r="I2" t="n">
         <v>37250</v>
@@ -533,7 +533,7 @@
         <v>200</v>
       </c>
       <c r="N2" t="n">
-        <v>14.12</v>
+        <v>14.12000000000001</v>
       </c>
     </row>
     <row r="3">
